--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325611</v>
+        <v>123325609</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602011</v>
+        <v>601993</v>
       </c>
       <c r="R2" t="n">
-        <v>6901460</v>
+        <v>6901464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325616</v>
+        <v>123325614</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>91679</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602001</v>
+        <v>602022</v>
       </c>
       <c r="R3" t="n">
-        <v>6901383</v>
+        <v>6901451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325614</v>
+        <v>123325616</v>
       </c>
       <c r="B4" t="n">
-        <v>91676</v>
+        <v>79387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +957,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +985,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602022</v>
+        <v>602001</v>
       </c>
       <c r="R4" t="n">
-        <v>6901451</v>
+        <v>6901383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1078,7 @@
         <v>123325613</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325609</v>
+        <v>123325611</v>
       </c>
       <c r="B6" t="n">
-        <v>98386</v>
+        <v>98285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601993</v>
+        <v>602011</v>
       </c>
       <c r="R6" t="n">
-        <v>6901464</v>
+        <v>6901460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325609</v>
+        <v>123325616</v>
       </c>
       <c r="B2" t="n">
-        <v>98389</v>
+        <v>79389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601993</v>
+        <v>602001</v>
       </c>
       <c r="R2" t="n">
-        <v>6901464</v>
+        <v>6901383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sumpskogn</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325614</v>
+        <v>123325613</v>
       </c>
       <c r="B3" t="n">
-        <v>91679</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602022</v>
+        <v>601977</v>
       </c>
       <c r="R3" t="n">
-        <v>6901451</v>
+        <v>6901465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325616</v>
+        <v>123325611</v>
       </c>
       <c r="B4" t="n">
-        <v>79387</v>
+        <v>98287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +947,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602001</v>
+        <v>602011</v>
       </c>
       <c r="R4" t="n">
-        <v>6901383</v>
+        <v>6901460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325613</v>
+        <v>123325614</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>91681</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1105</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1113,16 +1108,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601977</v>
+        <v>602022</v>
       </c>
       <c r="R5" t="n">
-        <v>6901465</v>
+        <v>6901451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325611</v>
+        <v>123325609</v>
       </c>
       <c r="B6" t="n">
-        <v>98285</v>
+        <v>98391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602011</v>
+        <v>601993</v>
       </c>
       <c r="R6" t="n">
-        <v>6901460</v>
+        <v>6901464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325616</v>
       </c>
       <c r="B2" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325611</v>
+        <v>123325614</v>
       </c>
       <c r="B4" t="n">
-        <v>98287</v>
+        <v>91687</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,35 +947,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602011</v>
+        <v>602022</v>
       </c>
       <c r="R4" t="n">
-        <v>6901460</v>
+        <v>6901451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325614</v>
+        <v>123325609</v>
       </c>
       <c r="B5" t="n">
-        <v>91681</v>
+        <v>98397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,35 +1082,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1105</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602022</v>
+        <v>601993</v>
       </c>
       <c r="R5" t="n">
-        <v>6901451</v>
+        <v>6901464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325609</v>
+        <v>123325611</v>
       </c>
       <c r="B6" t="n">
-        <v>98391</v>
+        <v>98293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601993</v>
+        <v>602011</v>
       </c>
       <c r="R6" t="n">
-        <v>6901464</v>
+        <v>6901460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325616</v>
+        <v>123325614</v>
       </c>
       <c r="B2" t="n">
-        <v>79390</v>
+        <v>91690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602001</v>
+        <v>602022</v>
       </c>
       <c r="R2" t="n">
-        <v>6901383</v>
+        <v>6901451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325614</v>
+        <v>123325611</v>
       </c>
       <c r="B4" t="n">
-        <v>91687</v>
+        <v>98296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602022</v>
+        <v>602011</v>
       </c>
       <c r="R4" t="n">
-        <v>6901451</v>
+        <v>6901460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1073,7 +1078,7 @@
         <v>123325609</v>
       </c>
       <c r="B5" t="n">
-        <v>98397</v>
+        <v>98400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325611</v>
+        <v>123325616</v>
       </c>
       <c r="B6" t="n">
-        <v>98293</v>
+        <v>79393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1222,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602011</v>
+        <v>602001</v>
       </c>
       <c r="R6" t="n">
-        <v>6901460</v>
+        <v>6901383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325614</v>
+        <v>123325611</v>
       </c>
       <c r="B2" t="n">
-        <v>91690</v>
+        <v>98313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1105</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602022</v>
+        <v>602011</v>
       </c>
       <c r="R2" t="n">
-        <v>6901451</v>
+        <v>6901460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325613</v>
+        <v>123325614</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>91707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,16 +848,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601977</v>
+        <v>602022</v>
       </c>
       <c r="R3" t="n">
-        <v>6901465</v>
+        <v>6901451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325611</v>
+        <v>123325613</v>
       </c>
       <c r="B4" t="n">
-        <v>98296</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,35 +957,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602011</v>
+        <v>601977</v>
       </c>
       <c r="R4" t="n">
-        <v>6901460</v>
+        <v>6901465</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1078,7 @@
         <v>123325609</v>
       </c>
       <c r="B5" t="n">
-        <v>98400</v>
+        <v>98417</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>123325616</v>
       </c>
       <c r="B6" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325611</v>
+        <v>123325613</v>
       </c>
       <c r="B2" t="n">
-        <v>98313</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602011</v>
+        <v>601977</v>
       </c>
       <c r="R2" t="n">
-        <v>6901460</v>
+        <v>6901465</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325614</v>
+        <v>123325616</v>
       </c>
       <c r="B3" t="n">
-        <v>91707</v>
+        <v>79404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602022</v>
+        <v>602001</v>
       </c>
       <c r="R3" t="n">
-        <v>6901451</v>
+        <v>6901383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325613</v>
+        <v>123325614</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>91712</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,16 +973,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601977</v>
+        <v>602022</v>
       </c>
       <c r="R4" t="n">
-        <v>6901465</v>
+        <v>6901451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325609</v>
+        <v>123325611</v>
       </c>
       <c r="B5" t="n">
-        <v>98417</v>
+        <v>98419</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601993</v>
+        <v>602011</v>
       </c>
       <c r="R5" t="n">
-        <v>6901464</v>
+        <v>6901460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325616</v>
+        <v>123325609</v>
       </c>
       <c r="B6" t="n">
-        <v>79399</v>
+        <v>98523</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,35 +1217,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602001</v>
+        <v>601993</v>
       </c>
       <c r="R6" t="n">
-        <v>6901383</v>
+        <v>6901464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,7 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325613</v>
+        <v>123325611</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601977</v>
+        <v>602011</v>
       </c>
       <c r="R2" t="n">
-        <v>6901465</v>
+        <v>6901460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325616</v>
+        <v>123325614</v>
       </c>
       <c r="B3" t="n">
-        <v>79404</v>
+        <v>91714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +850,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602001</v>
+        <v>602022</v>
       </c>
       <c r="R3" t="n">
-        <v>6901383</v>
+        <v>6901451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325614</v>
+        <v>123325609</v>
       </c>
       <c r="B4" t="n">
-        <v>91712</v>
+        <v>98525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602022</v>
+        <v>601993</v>
       </c>
       <c r="R4" t="n">
-        <v>6901451</v>
+        <v>6901464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325611</v>
+        <v>123325616</v>
       </c>
       <c r="B5" t="n">
-        <v>98419</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602011</v>
+        <v>602001</v>
       </c>
       <c r="R5" t="n">
-        <v>6901460</v>
+        <v>6901383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1179,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325609</v>
+        <v>123325613</v>
       </c>
       <c r="B6" t="n">
-        <v>98523</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1222,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601993</v>
+        <v>601977</v>
       </c>
       <c r="R6" t="n">
-        <v>6901464</v>
+        <v>6901465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325611</v>
+        <v>123325613</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602011</v>
+        <v>601977</v>
       </c>
       <c r="R2" t="n">
-        <v>6901460</v>
+        <v>6901465</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325614</v>
+        <v>123325609</v>
       </c>
       <c r="B3" t="n">
-        <v>91714</v>
+        <v>98100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602022</v>
+        <v>601993</v>
       </c>
       <c r="R3" t="n">
-        <v>6901451</v>
+        <v>6901464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325609</v>
+        <v>123325616</v>
       </c>
       <c r="B4" t="n">
-        <v>98525</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601993</v>
+        <v>602001</v>
       </c>
       <c r="R4" t="n">
-        <v>6901464</v>
+        <v>6901383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sumpskogn</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325616</v>
+        <v>123325614</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>91714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1105</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602001</v>
+        <v>602022</v>
       </c>
       <c r="R5" t="n">
-        <v>6901383</v>
+        <v>6901451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325613</v>
+        <v>123325611</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,30 +1217,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601977</v>
+        <v>602011</v>
       </c>
       <c r="R6" t="n">
-        <v>6901465</v>
+        <v>6901460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325613</v>
+        <v>123325609</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>98100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601977</v>
+        <v>601993</v>
       </c>
       <c r="R2" t="n">
-        <v>6901465</v>
+        <v>6901464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325609</v>
+        <v>123325616</v>
       </c>
       <c r="B3" t="n">
-        <v>98100</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601993</v>
+        <v>602001</v>
       </c>
       <c r="R3" t="n">
-        <v>6901464</v>
+        <v>6901383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sumpskogn</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325616</v>
+        <v>123325614</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>91714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602001</v>
+        <v>602022</v>
       </c>
       <c r="R4" t="n">
-        <v>6901383</v>
+        <v>6901451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325614</v>
+        <v>123325611</v>
       </c>
       <c r="B5" t="n">
-        <v>91714</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,35 +1087,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1105</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602022</v>
+        <v>602011</v>
       </c>
       <c r="R5" t="n">
-        <v>6901451</v>
+        <v>6901460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325611</v>
+        <v>123325613</v>
       </c>
       <c r="B6" t="n">
-        <v>97996</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1222,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602011</v>
+        <v>601977</v>
       </c>
       <c r="R6" t="n">
-        <v>6901460</v>
+        <v>6901465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325609</v>
+        <v>123325611</v>
       </c>
       <c r="B2" t="n">
-        <v>98100</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601993</v>
+        <v>602011</v>
       </c>
       <c r="R2" t="n">
-        <v>6901464</v>
+        <v>6901460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325616</v>
+        <v>123325613</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,21 +848,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602001</v>
+        <v>601977</v>
       </c>
       <c r="R3" t="n">
-        <v>6901383</v>
+        <v>6901465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325611</v>
+        <v>123325609</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>98100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602011</v>
+        <v>601993</v>
       </c>
       <c r="R5" t="n">
-        <v>6901460</v>
+        <v>6901464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325613</v>
+        <v>123325616</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1248,16 +1248,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601977</v>
+        <v>602001</v>
       </c>
       <c r="R6" t="n">
-        <v>6901465</v>
+        <v>6901383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I sumpskog</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325613</v>
+        <v>123325614</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>91714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,16 +848,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601977</v>
+        <v>602022</v>
       </c>
       <c r="R3" t="n">
-        <v>6901465</v>
+        <v>6901451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325614</v>
+        <v>123325616</v>
       </c>
       <c r="B4" t="n">
-        <v>91714</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +957,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +985,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602022</v>
+        <v>602001</v>
       </c>
       <c r="R4" t="n">
-        <v>6901451</v>
+        <v>6901383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på tall</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325609</v>
+        <v>123325613</v>
       </c>
       <c r="B5" t="n">
-        <v>98100</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,35 +1087,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601993</v>
+        <v>601977</v>
       </c>
       <c r="R5" t="n">
-        <v>6901464</v>
+        <v>6901465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpskogn</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325616</v>
+        <v>123325609</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>98100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,35 +1217,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602001</v>
+        <v>601993</v>
       </c>
       <c r="R6" t="n">
-        <v>6901383</v>
+        <v>6901464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,7 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 42153-2023 artfynd.xlsx
+++ b/artfynd/A 42153-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325611</v>
+        <v>123325614</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
+        <v>91714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602011</v>
+        <v>602022</v>
       </c>
       <c r="R2" t="n">
-        <v>6901460</v>
+        <v>6901451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1403</t>
+          <t>2024_1401</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325614</v>
+        <v>123325613</v>
       </c>
       <c r="B3" t="n">
-        <v>91714</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,21 +848,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602022</v>
+        <v>601977</v>
       </c>
       <c r="R3" t="n">
-        <v>6901451</v>
+        <v>6901465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1401</t>
+          <t>2024_1402</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>I sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325616</v>
+        <v>123325611</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +952,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602001</v>
+        <v>602011</v>
       </c>
       <c r="R4" t="n">
-        <v>6901383</v>
+        <v>6901460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1400</t>
+          <t>2024_1403</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325613</v>
+        <v>123325609</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>98100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,30 +1087,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601977</v>
+        <v>601993</v>
       </c>
       <c r="R5" t="n">
-        <v>6901465</v>
+        <v>6901464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1402</t>
+          <t>2024_1404</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I sumpskog</t>
+          <t>Sumpskogn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325609</v>
+        <v>123325616</v>
       </c>
       <c r="B6" t="n">
-        <v>98100</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1222,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601993</v>
+        <v>602001</v>
       </c>
       <c r="R6" t="n">
-        <v>6901464</v>
+        <v>6901383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1289,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1404</t>
+          <t>2024_1400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sumpskogn</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
